--- a/CmdScript/SimulRadio_StationList.xlsx
+++ b/CmdScript/SimulRadio_StationList.xlsx
@@ -3387,7 +3387,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Fm-yonabaru</t>
+    <t xml:space="preserve">fm-yonabaru</t>
   </si>
   <si>
     <r>
